--- a/results/final_0624_summary/HumanPseAAC_BinaryVector_summary.xlsx
+++ b/results/final_0624_summary/HumanPseAAC_BinaryVector_summary.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U12"/>
+  <dimension ref="A1:BE15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,80 +456,260 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>example_precision__0.0</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>example_precision__0.1</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>example_precision__0.2</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>example_precision__0.3</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>example_recall__0.0</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>example_recall__0.1</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>example_recall__0.2</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>example_recall__0.3</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
           <t>f1__0.0</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>f1__0.1</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>f1__0.2</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>f1__0.3</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>hamming_accuracy__0.0</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>hamming_accuracy__0.1</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>hamming_accuracy__0.2</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>hamming_accuracy__0.3</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>jaccard__0.0</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>jaccard__0.1</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>jaccard__0.2</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>jaccard__0.3</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>macro_f1__0.0</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>macro_f1__0.1</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>macro_f1__0.2</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>macro_f1__0.3</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>macro_precision__0.0</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>macro_precision__0.1</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>macro_precision__0.2</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>macro_precision__0.3</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>macro_recall__0.0</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>macro_recall__0.1</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>macro_recall__0.2</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>macro_recall__0.3</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>mfrd__0.0</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>mfrd__0.1</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>mfrd__0.2</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>mfrd__0.3</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>micro_f1__0.0</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>micro_f1__0.1</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>micro_f1__0.2</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>micro_f1__0.3</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>micro_precision__0.0</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>micro_precision__0.1</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>micro_precision__0.2</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>micro_precision__0.3</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>micro_recall__0.0</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>micro_recall__0.1</t>
+        </is>
+      </c>
+      <c r="AZ1" s="1" t="inlineStr">
+        <is>
+          <t>micro_recall__0.2</t>
+        </is>
+      </c>
+      <c r="BA1" s="1" t="inlineStr">
+        <is>
+          <t>micro_recall__0.3</t>
+        </is>
+      </c>
+      <c r="BB1" s="1" t="inlineStr">
         <is>
           <t>subset0_1__0.0</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="BC1" s="1" t="inlineStr">
         <is>
           <t>subset0_1__0.1</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="BD1" s="1" t="inlineStr">
         <is>
           <t>subset0_1__0.2</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="BE1" s="1" t="inlineStr">
         <is>
           <t>subset0_1__0.3</t>
         </is>
@@ -563,80 +743,260 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
+          <t>0.1254±0.0066</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0.1045±0.0076</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>0.0924±0.0021</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>0.0887±0.0011</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>0.9333±0.0036</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>0.9562±0.0046</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>0.9708±0.0070</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>0.9658±0.0073</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
           <t>0.1932±0.0066</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>0.1766±0.0073</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>0.1655±0.0027</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>0.1608±0.0017</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>0.2029±0.0090</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>0.1763±0.0143</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>0.1557±0.0092</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>0.1491±0.0057</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>0.1231±0.0063</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>0.1036±0.0070</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>0.0923±0.0020</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>0.0886±0.0010</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>0.1477±0.0019</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>0.1468±0.0020</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>0.1459±0.0022</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>0.1441±0.0015</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>0.0886±0.0012</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>0.0875±0.0012</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>0.0868±0.0012</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>0.0857±0.0009</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>0.9191±0.0095</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>0.9428±0.0116</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>0.9561±0.0250</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>0.9449±0.0245</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr">
         <is>
           <t>0.9735±0.0065</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="AM2" t="inlineStr">
         <is>
           <t>0.9836±0.0039</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="AN2" t="inlineStr">
         <is>
           <t>0.9795±0.0091</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="AO2" t="inlineStr">
         <is>
           <t>0.9749±0.0095</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>0.1650±0.0019</t>
+        </is>
+      </c>
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>0.1641±0.0027</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>0.1628±0.0022</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>0.1611±0.0016</t>
+        </is>
+      </c>
+      <c r="AT2" t="inlineStr">
+        <is>
+          <t>0.0905±0.0011</t>
+        </is>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>0.0898±0.0016</t>
+        </is>
+      </c>
+      <c r="AV2" t="inlineStr">
+        <is>
+          <t>0.0888±0.0013</t>
+        </is>
+      </c>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>0.0879±0.0009</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>0.9304±0.0044</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>0.9550±0.0048</t>
+        </is>
+      </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>0.9694±0.0067</t>
+        </is>
+      </c>
+      <c r="BA2" t="inlineStr">
+        <is>
+          <t>0.9654±0.0061</t>
+        </is>
+      </c>
+      <c r="BB2" t="inlineStr">
         <is>
           <t>0.0319±0.0065</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="BC2" t="inlineStr">
         <is>
           <t>0.0098±0.0063</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
+      <c r="BD2" t="inlineStr">
         <is>
           <t>0.0011±0.0014</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="BE2" t="inlineStr">
         <is>
           <t>0.0000±0.0000</t>
         </is>
@@ -670,80 +1030,260 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
+          <t>0.1255±0.0065</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0.1046±0.0076</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0.0924±0.0021</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>0.0887±0.0010</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>0.9336±0.0034</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0.9565±0.0049</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>0.9712±0.0065</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>0.9661±0.0073</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
           <t>0.1934±0.0065</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>0.1767±0.0072</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>0.1656±0.0027</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>0.1608±0.0017</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>0.2029±0.0090</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>0.1763±0.0142</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>0.1557±0.0092</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>0.1489±0.0057</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>0.1232±0.0063</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>0.1037±0.0070</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>0.0923±0.0020</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>0.0886±0.0010</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>0.1478±0.0019</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>0.1468±0.0020</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>0.1459±0.0022</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>0.1441±0.0015</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>0.0886±0.0012</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>0.0876±0.0012</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>0.0868±0.0012</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>0.0857±0.0009</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>0.9192±0.0095</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>0.9429±0.0116</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>0.9563±0.0250</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>0.9450±0.0244</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr">
         <is>
           <t>0.9745±0.0074</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="AM3" t="inlineStr">
         <is>
           <t>0.9839±0.0041</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="AN3" t="inlineStr">
         <is>
           <t>0.9798±0.0094</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="AO3" t="inlineStr">
         <is>
           <t>0.9751±0.0092</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>0.1651±0.0019</t>
+        </is>
+      </c>
+      <c r="AQ3" t="inlineStr">
+        <is>
+          <t>0.1642±0.0027</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>0.1628±0.0022</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>0.1611±0.0016</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr">
+        <is>
+          <t>0.0906±0.0011</t>
+        </is>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>0.0898±0.0016</t>
+        </is>
+      </c>
+      <c r="AV3" t="inlineStr">
+        <is>
+          <t>0.0889±0.0013</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>0.0879±0.0009</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>0.9307±0.0042</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>0.9553±0.0050</t>
+        </is>
+      </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>0.9698±0.0063</t>
+        </is>
+      </c>
+      <c r="BA3" t="inlineStr">
+        <is>
+          <t>0.9657±0.0061</t>
+        </is>
+      </c>
+      <c r="BB3" t="inlineStr">
         <is>
           <t>0.0319±0.0065</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
+      <c r="BC3" t="inlineStr">
         <is>
           <t>0.0098±0.0063</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="BD3" t="inlineStr">
         <is>
           <t>0.0011±0.0014</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="BE3" t="inlineStr">
         <is>
           <t>0.0000±0.0000</t>
         </is>
@@ -777,80 +1317,260 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
+          <t>0.1254±0.0066</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0.1045±0.0076</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0.0924±0.0021</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>0.0888±0.0011</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>0.9333±0.0036</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>0.9562±0.0046</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>0.9708±0.0069</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>0.9659±0.0073</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
           <t>0.1932±0.0066</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>0.1766±0.0073</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>0.1655±0.0027</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="Q4" t="inlineStr">
         <is>
           <t>0.1608±0.0017</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>0.2029±0.0090</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>0.1763±0.0143</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>0.1557±0.0091</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>0.1491±0.0056</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>0.1231±0.0063</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>0.1036±0.0070</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>0.0923±0.0020</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>0.0887±0.0011</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>0.1477±0.0019</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>0.1468±0.0020</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>0.1459±0.0022</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>0.1441±0.0015</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>0.0886±0.0012</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>0.0875±0.0012</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>0.0868±0.0012</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>0.0857±0.0009</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>0.9191±0.0095</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>0.9428±0.0116</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>0.9562±0.0251</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>0.9450±0.0247</t>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr">
         <is>
           <t>0.9735±0.0065</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="AM4" t="inlineStr">
         <is>
           <t>0.9836±0.0039</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="AN4" t="inlineStr">
         <is>
           <t>0.9795±0.0091</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr">
+      <c r="AO4" t="inlineStr">
         <is>
           <t>0.9756±0.0092</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="AP4" t="inlineStr">
+        <is>
+          <t>0.1650±0.0019</t>
+        </is>
+      </c>
+      <c r="AQ4" t="inlineStr">
+        <is>
+          <t>0.1641±0.0027</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>0.1628±0.0022</t>
+        </is>
+      </c>
+      <c r="AS4" t="inlineStr">
+        <is>
+          <t>0.1612±0.0016</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr">
+        <is>
+          <t>0.0905±0.0011</t>
+        </is>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
+          <t>0.0898±0.0016</t>
+        </is>
+      </c>
+      <c r="AV4" t="inlineStr">
+        <is>
+          <t>0.0888±0.0013</t>
+        </is>
+      </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>0.0879±0.0009</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>0.9304±0.0044</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>0.9550±0.0048</t>
+        </is>
+      </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>0.9694±0.0067</t>
+        </is>
+      </c>
+      <c r="BA4" t="inlineStr">
+        <is>
+          <t>0.9656±0.0061</t>
+        </is>
+      </c>
+      <c r="BB4" t="inlineStr">
         <is>
           <t>0.0319±0.0065</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
+      <c r="BC4" t="inlineStr">
         <is>
           <t>0.0098±0.0063</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr">
+      <c r="BD4" t="inlineStr">
         <is>
           <t>0.0011±0.0014</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="BE4" t="inlineStr">
         <is>
           <t>0.0000±0.0000</t>
         </is>
@@ -884,80 +1604,260 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
+          <t>0.1255±0.0065</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0.1046±0.0076</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0.0925±0.0021</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>0.0888±0.0011</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>0.9336±0.0034</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0.9565±0.0049</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>0.9713±0.0065</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>0.9662±0.0073</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
           <t>0.1934±0.0065</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>0.1767±0.0072</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>0.1656±0.0027</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t>0.1609±0.0017</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="R5" t="inlineStr">
         <is>
           <t>0.2029±0.0090</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>0.1763±0.0142</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>0.1556±0.0091</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>0.1489±0.0056</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>0.1232±0.0063</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>0.1037±0.0070</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>0.0923±0.0020</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>0.0887±0.0010</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>0.1478±0.0019</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>0.1468±0.0020</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>0.1459±0.0022</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>0.1441±0.0015</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>0.0886±0.0012</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>0.0876±0.0012</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>0.0868±0.0013</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>0.0857±0.0009</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>0.9192±0.0095</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>0.9429±0.0116</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>0.9564±0.0250</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>0.9451±0.0247</t>
+        </is>
+      </c>
+      <c r="AL5" t="inlineStr">
         <is>
           <t>0.9745±0.0074</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="AM5" t="inlineStr">
         <is>
           <t>0.9839±0.0041</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="AN5" t="inlineStr">
         <is>
           <t>0.9798±0.0094</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="AO5" t="inlineStr">
         <is>
           <t>0.9758±0.0089</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="AP5" t="inlineStr">
+        <is>
+          <t>0.1651±0.0019</t>
+        </is>
+      </c>
+      <c r="AQ5" t="inlineStr">
+        <is>
+          <t>0.1642±0.0027</t>
+        </is>
+      </c>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>0.1628±0.0022</t>
+        </is>
+      </c>
+      <c r="AS5" t="inlineStr">
+        <is>
+          <t>0.1612±0.0016</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr">
+        <is>
+          <t>0.0906±0.0011</t>
+        </is>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
+          <t>0.0898±0.0016</t>
+        </is>
+      </c>
+      <c r="AV5" t="inlineStr">
+        <is>
+          <t>0.0889±0.0013</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>0.0879±0.0009</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>0.9307±0.0042</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>0.9553±0.0050</t>
+        </is>
+      </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>0.9700±0.0063</t>
+        </is>
+      </c>
+      <c r="BA5" t="inlineStr">
+        <is>
+          <t>0.9659±0.0061</t>
+        </is>
+      </c>
+      <c r="BB5" t="inlineStr">
         <is>
           <t>0.0319±0.0065</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="BC5" t="inlineStr">
         <is>
           <t>0.0098±0.0063</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="BD5" t="inlineStr">
         <is>
           <t>0.0011±0.0014</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="BE5" t="inlineStr">
         <is>
           <t>0.0000±0.0000</t>
         </is>
@@ -991,80 +1891,260 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
+          <t>0.1234±0.0066</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0.1161±0.0105</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>0.1138±0.0070</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>0.1212±0.0064</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>0.9083±0.0063</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>0.8968±0.0058</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>0.8728±0.0094</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>0.8026±0.0135</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
           <t>0.1896±0.0062</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>0.1845±0.0097</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>0.1869±0.0073</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>0.2010±0.0071</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="R6" t="inlineStr">
         <is>
           <t>0.2103±0.0085</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>0.2232±0.0155</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>0.2795±0.0200</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>0.4127±0.0174</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>0.1207±0.0057</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>0.1141±0.0094</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>0.1121±0.0065</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>0.1196±0.0064</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>0.1464±0.0014</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>0.1459±0.0023</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>0.1482±0.0027</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>0.1513±0.0023</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>0.0882±0.0007</t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>0.0880±0.0013</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>0.0900±0.0016</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>0.0933±0.0011</t>
+        </is>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>0.8942±0.0162</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>0.8873±0.0178</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>0.8348±0.0241</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>0.7024±0.0429</t>
+        </is>
+      </c>
+      <c r="AL6" t="inlineStr">
         <is>
           <t>0.9633±0.0108</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="AM6" t="inlineStr">
         <is>
           <t>0.9445±0.0138</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="AN6" t="inlineStr">
         <is>
           <t>0.9065±0.0243</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr">
+      <c r="AO6" t="inlineStr">
         <is>
           <t>0.8288±0.0525</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="AP6" t="inlineStr">
+        <is>
+          <t>0.1624±0.0012</t>
+        </is>
+      </c>
+      <c r="AQ6" t="inlineStr">
+        <is>
+          <t>0.1632±0.0028</t>
+        </is>
+      </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>0.1696±0.0032</t>
+        </is>
+      </c>
+      <c r="AS6" t="inlineStr">
+        <is>
+          <t>0.1876±0.0038</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr">
+        <is>
+          <t>0.0892±0.0007</t>
+        </is>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>0.0898±0.0017</t>
+        </is>
+      </c>
+      <c r="AV6" t="inlineStr">
+        <is>
+          <t>0.0940±0.0020</t>
+        </is>
+      </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>0.1062±0.0024</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>0.9047±0.0040</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>0.8945±0.0059</t>
+        </is>
+      </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>0.8690±0.0106</t>
+        </is>
+      </c>
+      <c r="BA6" t="inlineStr">
+        <is>
+          <t>0.8005±0.0119</t>
+        </is>
+      </c>
+      <c r="BB6" t="inlineStr">
         <is>
           <t>0.0306±0.0043</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
+      <c r="BC6" t="inlineStr">
         <is>
           <t>0.0217±0.0072</t>
         </is>
       </c>
-      <c r="T6" t="inlineStr">
+      <c r="BD6" t="inlineStr">
         <is>
           <t>0.0118±0.0039</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
+      <c r="BE6" t="inlineStr">
         <is>
           <t>0.0045±0.0034</t>
         </is>
@@ -1098,80 +2178,260 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
+          <t>0.1245±0.0064</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0.1173±0.0103</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>0.1149±0.0076</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>0.1205±0.0047</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>0.9096±0.0052</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>0.8973±0.0072</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>0.8774±0.0088</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>0.8185±0.0101</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
           <t>0.1907±0.0061</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>0.1859±0.0094</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>0.1892±0.0081</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>0.2027±0.0056</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="R7" t="inlineStr">
         <is>
           <t>0.2123±0.0084</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>0.2262±0.0157</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>0.2844±0.0204</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>0.4145±0.0162</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>0.1218±0.0056</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>0.1152±0.0092</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>0.1134±0.0070</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>0.1194±0.0048</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>0.1467±0.0014</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>0.1461±0.0022</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>0.1489±0.0029</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>0.1521±0.0023</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>0.0884±0.0007</t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>0.0881±0.0013</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>0.0903±0.0017</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>0.0933±0.0011</t>
+        </is>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>0.8933±0.0174</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>0.8856±0.0167</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>0.8333±0.0242</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>0.7072±0.0410</t>
+        </is>
+      </c>
+      <c r="AL7" t="inlineStr">
         <is>
           <t>0.9652±0.0111</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="AM7" t="inlineStr">
         <is>
           <t>0.9477±0.0137</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="AN7" t="inlineStr">
         <is>
           <t>0.9177±0.0231</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr">
+      <c r="AO7" t="inlineStr">
         <is>
           <t>0.8596±0.0470</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="AP7" t="inlineStr">
+        <is>
+          <t>0.1630±0.0012</t>
+        </is>
+      </c>
+      <c r="AQ7" t="inlineStr">
+        <is>
+          <t>0.1638±0.0028</t>
+        </is>
+      </c>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>0.1714±0.0035</t>
+        </is>
+      </c>
+      <c r="AS7" t="inlineStr">
+        <is>
+          <t>0.1913±0.0038</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr">
+        <is>
+          <t>0.0895±0.0007</t>
+        </is>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
+          <t>0.0901±0.0017</t>
+        </is>
+      </c>
+      <c r="AV7" t="inlineStr">
+        <is>
+          <t>0.0951±0.0022</t>
+        </is>
+      </c>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>0.1083±0.0024</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>0.9057±0.0034</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>0.8949±0.0061</t>
+        </is>
+      </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>0.8742±0.0092</t>
+        </is>
+      </c>
+      <c r="BA7" t="inlineStr">
+        <is>
+          <t>0.8175±0.0111</t>
+        </is>
+      </c>
+      <c r="BB7" t="inlineStr">
         <is>
           <t>0.0316±0.0039</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
+      <c r="BC7" t="inlineStr">
         <is>
           <t>0.0224±0.0071</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
+      <c r="BD7" t="inlineStr">
         <is>
           <t>0.0111±0.0042</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr">
+      <c r="BE7" t="inlineStr">
         <is>
           <t>0.0018±0.0022</t>
         </is>
@@ -1205,80 +2465,260 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
+          <t>0.1230±0.0065</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>0.1161±0.0107</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>0.1135±0.0071</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>0.1209±0.0064</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>0.9079±0.0072</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>0.8965±0.0060</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>0.8718±0.0100</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>0.7998±0.0148</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
           <t>0.1892±0.0062</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>0.1844±0.0099</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>0.1864±0.0073</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>0.2002±0.0068</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="R8" t="inlineStr">
         <is>
           <t>0.2096±0.0086</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>0.2220±0.0155</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>0.2784±0.0203</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>0.4117±0.0172</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>0.1204±0.0056</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>0.1142±0.0096</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>0.1118±0.0065</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>0.1192±0.0061</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>0.1463±0.0014</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>0.1457±0.0023</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>0.1481±0.0027</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>0.1509±0.0024</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>0.0881±0.0007</t>
+        </is>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>0.0879±0.0014</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>0.0899±0.0015</t>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>0.0932±0.0012</t>
+        </is>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>0.8941±0.0163</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>0.8870±0.0173</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>0.8356±0.0239</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>0.7007±0.0436</t>
+        </is>
+      </c>
+      <c r="AL8" t="inlineStr">
         <is>
           <t>0.9633±0.0108</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="AM8" t="inlineStr">
         <is>
           <t>0.9444±0.0138</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="AN8" t="inlineStr">
         <is>
           <t>0.9033±0.0266</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="AO8" t="inlineStr">
         <is>
           <t>0.8252±0.0512</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="AP8" t="inlineStr">
+        <is>
+          <t>0.1622±0.0012</t>
+        </is>
+      </c>
+      <c r="AQ8" t="inlineStr">
+        <is>
+          <t>0.1629±0.0029</t>
+        </is>
+      </c>
+      <c r="AR8" t="inlineStr">
+        <is>
+          <t>0.1692±0.0032</t>
+        </is>
+      </c>
+      <c r="AS8" t="inlineStr">
+        <is>
+          <t>0.1867±0.0038</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr">
+        <is>
+          <t>0.0891±0.0007</t>
+        </is>
+      </c>
+      <c r="AU8" t="inlineStr">
+        <is>
+          <t>0.0896±0.0018</t>
+        </is>
+      </c>
+      <c r="AV8" t="inlineStr">
+        <is>
+          <t>0.0938±0.0020</t>
+        </is>
+      </c>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>0.1058±0.0024</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>0.9041±0.0045</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>0.8939±0.0059</t>
+        </is>
+      </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>0.8680±0.0109</t>
+        </is>
+      </c>
+      <c r="BA8" t="inlineStr">
+        <is>
+          <t>0.7975±0.0139</t>
+        </is>
+      </c>
+      <c r="BB8" t="inlineStr">
         <is>
           <t>0.0303±0.0039</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="BC8" t="inlineStr">
         <is>
           <t>0.0221±0.0076</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
+      <c r="BD8" t="inlineStr">
         <is>
           <t>0.0118±0.0041</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
+      <c r="BE8" t="inlineStr">
         <is>
           <t>0.0045±0.0031</t>
         </is>
@@ -1312,80 +2752,260 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
+          <t>0.1242±0.0065</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0.1172±0.0107</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>0.1144±0.0073</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>0.1198±0.0044</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>0.9083±0.0059</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>0.8974±0.0066</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>0.8764±0.0090</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>0.8163±0.0140</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
           <t>0.1904±0.0062</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="O9" t="inlineStr">
         <is>
           <t>0.1858±0.0099</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>0.1887±0.0077</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="Q9" t="inlineStr">
         <is>
           <t>0.2017±0.0053</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="R9" t="inlineStr">
         <is>
           <t>0.2121±0.0082</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>0.2256±0.0157</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>0.2842±0.0203</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>0.4125±0.0164</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>0.1216±0.0057</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>0.1153±0.0096</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>0.1129±0.0067</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>0.1187±0.0045</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>0.1465±0.0015</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>0.1461±0.0023</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>0.1488±0.0029</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>0.1517±0.0026</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>0.0883±0.0007</t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>0.0881±0.0013</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>0.0902±0.0017</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t>0.0932±0.0013</t>
+        </is>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>0.8958±0.0164</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>0.8873±0.0152</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>0.8334±0.0245</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>0.7038±0.0454</t>
+        </is>
+      </c>
+      <c r="AL9" t="inlineStr">
         <is>
           <t>0.9652±0.0111</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="AM9" t="inlineStr">
         <is>
           <t>0.9479±0.0108</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="AN9" t="inlineStr">
         <is>
           <t>0.9150±0.0240</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr">
+      <c r="AO9" t="inlineStr">
         <is>
           <t>0.8538±0.0465</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="AP9" t="inlineStr">
+        <is>
+          <t>0.1628±0.0012</t>
+        </is>
+      </c>
+      <c r="AQ9" t="inlineStr">
+        <is>
+          <t>0.1638±0.0030</t>
+        </is>
+      </c>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>0.1712±0.0035</t>
+        </is>
+      </c>
+      <c r="AS9" t="inlineStr">
+        <is>
+          <t>0.1903±0.0037</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr">
+        <is>
+          <t>0.0894±0.0007</t>
+        </is>
+      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
+          <t>0.0901±0.0018</t>
+        </is>
+      </c>
+      <c r="AV9" t="inlineStr">
+        <is>
+          <t>0.0949±0.0022</t>
+        </is>
+      </c>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>0.1077±0.0023</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>0.9047±0.0039</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>0.8954±0.0059</t>
+        </is>
+      </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>0.8730±0.0097</t>
+        </is>
+      </c>
+      <c r="BA9" t="inlineStr">
+        <is>
+          <t>0.8152±0.0141</t>
+        </is>
+      </c>
+      <c r="BB9" t="inlineStr">
         <is>
           <t>0.0312±0.0042</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="BC9" t="inlineStr">
         <is>
           <t>0.0229±0.0076</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr">
+      <c r="BD9" t="inlineStr">
         <is>
           <t>0.0106±0.0039</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr">
+      <c r="BE9" t="inlineStr">
         <is>
           <t>0.0018±0.0022</t>
         </is>
@@ -1419,80 +3039,260 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
+          <t>0.0763±0.0099</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>0.0804±0.0117</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>0.0972±0.0190</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>0.1290±0.0199</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>0.0716±0.0087</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>0.0745±0.0101</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>0.0901±0.0176</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>0.1288±0.0190</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
           <t>0.0732±0.0091</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="O10" t="inlineStr">
         <is>
           <t>0.0761±0.0106</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>0.0915±0.0178</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="Q10" t="inlineStr">
         <is>
           <t>0.1243±0.0187</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="R10" t="inlineStr">
         <is>
           <t>0.9181±0.0015</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>0.9173±0.0016</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>0.9167±0.0020</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>0.9083±0.0024</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>0.0716±0.0087</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>0.0737±0.0101</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>0.0877±0.0169</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>0.1158±0.0173</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>0.0302±0.0040</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>0.0341±0.0043</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>0.0438±0.0077</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>0.0669±0.0077</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>0.1531±0.0498</t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>0.1917±0.0371</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>0.1875±0.0398</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>0.1582±0.0431</t>
+        </is>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>0.0188±0.0025</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>0.0212±0.0030</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>0.0276±0.0057</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>0.0465±0.0066</t>
+        </is>
+      </c>
+      <c r="AL10" t="inlineStr">
         <is>
           <t>1.0000±0.0000</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
+      <c r="AM10" t="inlineStr">
         <is>
           <t>1.0000±0.0000</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="AN10" t="inlineStr">
         <is>
           <t>1.0000±0.0000</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr">
+      <c r="AO10" t="inlineStr">
         <is>
           <t>0.9989±0.0007</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr">
+      <c r="AP10" t="inlineStr">
+        <is>
+          <t>0.1174±0.0148</t>
+        </is>
+      </c>
+      <c r="AQ10" t="inlineStr">
+        <is>
+          <t>0.1231±0.0176</t>
+        </is>
+      </c>
+      <c r="AR10" t="inlineStr">
+        <is>
+          <t>0.1459±0.0268</t>
+        </is>
+      </c>
+      <c r="AS10" t="inlineStr">
+        <is>
+          <t>0.1828±0.0209</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr">
+        <is>
+          <t>0.6636±0.0581</t>
+        </is>
+      </c>
+      <c r="AU10" t="inlineStr">
+        <is>
+          <t>0.6005±0.0402</t>
+        </is>
+      </c>
+      <c r="AV10" t="inlineStr">
+        <is>
+          <t>0.5507±0.0622</t>
+        </is>
+      </c>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>0.3738±0.0180</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>0.0644±0.0084</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>0.0687±0.0105</t>
+        </is>
+      </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>0.0844±0.0170</t>
+        </is>
+      </c>
+      <c r="BA10" t="inlineStr">
+        <is>
+          <t>0.1218±0.0182</t>
+        </is>
+      </c>
+      <c r="BB10" t="inlineStr">
         <is>
           <t>0.0670±0.0081</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="BC10" t="inlineStr">
         <is>
           <t>0.0665±0.0096</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
+      <c r="BD10" t="inlineStr">
         <is>
           <t>0.0765±0.0146</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
+      <c r="BE10" t="inlineStr">
         <is>
           <t>0.0918±0.0137</t>
         </is>
@@ -1526,80 +3326,260 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
+          <t>0.0937±0.0087</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>0.0875±0.0130</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>0.0997±0.0177</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>0.1318±0.0158</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>0.0857±0.0070</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>0.0810±0.0111</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>0.0922±0.0159</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>0.1313±0.0143</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
           <t>0.0883±0.0075</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="O11" t="inlineStr">
         <is>
           <t>0.0829±0.0117</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="P11" t="inlineStr">
         <is>
           <t>0.0938±0.0163</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="Q11" t="inlineStr">
         <is>
           <t>0.1270±0.0143</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="R11" t="inlineStr">
         <is>
           <t>0.9184±0.0013</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="S11" t="inlineStr">
         <is>
           <t>0.9177±0.0014</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="T11" t="inlineStr">
         <is>
           <t>0.9163±0.0023</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="U11" t="inlineStr">
         <is>
           <t>0.9093±0.0025</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>0.0857±0.0070</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>0.0802±0.0110</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>0.0899±0.0154</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>0.1187±0.0138</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>0.0369±0.0037</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>0.0372±0.0054</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>0.0476±0.0073</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>0.0675±0.0061</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>0.1914±0.0277</t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>0.2009±0.0278</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>0.1792±0.0300</t>
+        </is>
+      </c>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>0.1536±0.0216</t>
+        </is>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>0.0239±0.0026</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>0.0233±0.0037</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>0.0301±0.0053</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>0.0465±0.0042</t>
+        </is>
+      </c>
+      <c r="AL11" t="inlineStr">
         <is>
           <t>1.0000±0.0000</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
+      <c r="AM11" t="inlineStr">
         <is>
           <t>1.0000±0.0000</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr">
+      <c r="AN11" t="inlineStr">
         <is>
           <t>1.0000±0.0000</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr">
+      <c r="AO11" t="inlineStr">
         <is>
           <t>0.9992±0.0011</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr">
+      <c r="AP11" t="inlineStr">
+        <is>
+          <t>0.1413±0.0127</t>
+        </is>
+      </c>
+      <c r="AQ11" t="inlineStr">
+        <is>
+          <t>0.1328±0.0187</t>
+        </is>
+      </c>
+      <c r="AR11" t="inlineStr">
+        <is>
+          <t>0.1487±0.0245</t>
+        </is>
+      </c>
+      <c r="AS11" t="inlineStr">
+        <is>
+          <t>0.1881±0.0187</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr">
+        <is>
+          <t>0.6477±0.0405</t>
+        </is>
+      </c>
+      <c r="AU11" t="inlineStr">
+        <is>
+          <t>0.6125±0.0392</t>
+        </is>
+      </c>
+      <c r="AV11" t="inlineStr">
+        <is>
+          <t>0.5348±0.0519</t>
+        </is>
+      </c>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>0.3883±0.0338</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>0.0794±0.0077</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>0.0746±0.0115</t>
+        </is>
+      </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>0.0866±0.0157</t>
+        </is>
+      </c>
+      <c r="BA11" t="inlineStr">
+        <is>
+          <t>0.1243±0.0136</t>
+        </is>
+      </c>
+      <c r="BB11" t="inlineStr">
         <is>
           <t>0.0782±0.0058</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
+      <c r="BC11" t="inlineStr">
         <is>
           <t>0.0723±0.0091</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr">
+      <c r="BD11" t="inlineStr">
         <is>
           <t>0.0786±0.0130</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr">
+      <c r="BE11" t="inlineStr">
         <is>
           <t>0.0958±0.0126</t>
         </is>
@@ -1638,77 +3618,1118 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
+          <t>0.0125±0.0040</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>0.0197±0.0075</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>0.0199±0.0082</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>0.0000±0.0000</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>0.0118±0.0035</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>0.0188±0.0075</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>0.0188±0.0084</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>0.0000±0.0000</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
           <t>0.0120±0.0036</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="P12" t="inlineStr">
         <is>
           <t>0.0190±0.0074</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="Q12" t="inlineStr">
         <is>
           <t>0.0190±0.0081</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="R12" t="inlineStr">
         <is>
           <t>0.9153±0.0009</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="S12" t="inlineStr">
         <is>
           <t>0.9160±0.0010</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="T12" t="inlineStr">
         <is>
           <t>0.9162±0.0013</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="U12" t="inlineStr">
         <is>
           <t>0.9158±0.0013</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>0.0000±0.0000</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>0.0117±0.0035</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>0.0185±0.0073</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>0.0185±0.0080</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>0.0000±0.0000</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>0.0054±0.0019</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>0.0081±0.0030</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>0.0081±0.0031</t>
+        </is>
+      </c>
+      <c r="AD12" t="inlineStr">
+        <is>
+          <t>0.0000±0.0000</t>
+        </is>
+      </c>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t>0.0861±0.0470</t>
+        </is>
+      </c>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t>0.0842±0.0387</t>
+        </is>
+      </c>
+      <c r="AG12" t="inlineStr">
+        <is>
+          <t>0.0702±0.0298</t>
+        </is>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>0.0000±0.0000</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>0.0028±0.0010</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>0.0044±0.0017</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>0.0045±0.0019</t>
+        </is>
+      </c>
+      <c r="AL12" t="inlineStr">
         <is>
           <t>1.0000±0.0000</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
+      <c r="AM12" t="inlineStr">
         <is>
           <t>1.0000±0.0000</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr">
+      <c r="AN12" t="inlineStr">
         <is>
           <t>1.0000±0.0000</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr">
+      <c r="AO12" t="inlineStr">
         <is>
           <t>1.0000±0.0000</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr">
+      <c r="AP12" t="inlineStr">
         <is>
           <t>0.0000±0.0000</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
+      <c r="AQ12" t="inlineStr">
+        <is>
+          <t>0.0209±0.0065</t>
+        </is>
+      </c>
+      <c r="AR12" t="inlineStr">
+        <is>
+          <t>0.0328±0.0123</t>
+        </is>
+      </c>
+      <c r="AS12" t="inlineStr">
+        <is>
+          <t>0.0329±0.0136</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr">
+        <is>
+          <t>0.0000±0.0000</t>
+        </is>
+      </c>
+      <c r="AU12" t="inlineStr">
+        <is>
+          <t>0.7998±0.1282</t>
+        </is>
+      </c>
+      <c r="AV12" t="inlineStr">
+        <is>
+          <t>0.7556±0.1730</t>
+        </is>
+      </c>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>0.6534±0.1659</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>0.0000±0.0000</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>0.0106±0.0033</t>
+        </is>
+      </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>0.0169±0.0065</t>
+        </is>
+      </c>
+      <c r="BA12" t="inlineStr">
+        <is>
+          <t>0.0170±0.0072</t>
+        </is>
+      </c>
+      <c r="BB12" t="inlineStr">
+        <is>
+          <t>0.0000±0.0000</t>
+        </is>
+      </c>
+      <c r="BC12" t="inlineStr">
         <is>
           <t>0.0108±0.0033</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr">
+      <c r="BD12" t="inlineStr">
         <is>
           <t>0.0171±0.0072</t>
         </is>
       </c>
-      <c r="U12" t="inlineStr">
+      <c r="BE12" t="inlineStr">
         <is>
           <t>0.0171±0.0078</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>ecc</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>0.9777±0.0027</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>0.9794±0.0039</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>0.9767±0.0053</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>0.9625±0.0072</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>0.0763±0.0129</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>0.0697±0.0133</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>0.0724±0.0166</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>0.0987±0.0177</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>0.0708±0.0107</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>0.0648±0.0118</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>0.0675±0.0148</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>0.0938±0.0153</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>0.0727±0.0113</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>0.0663±0.0122</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>0.0687±0.0151</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>0.0942±0.0157</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>0.9182±0.0017</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>0.9178±0.0017</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>0.9175±0.0014</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>0.9164±0.0020</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>0.0708±0.0107</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>0.0644±0.0116</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>0.0665±0.0141</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>0.0907±0.0147</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>0.0292±0.0042</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>0.0274±0.0064</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>0.0305±0.0067</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>0.0454±0.0101</t>
+        </is>
+      </c>
+      <c r="AD13" t="inlineStr">
+        <is>
+          <t>0.1767±0.0441</t>
+        </is>
+      </c>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t>0.1713±0.0659</t>
+        </is>
+      </c>
+      <c r="AF13" t="inlineStr">
+        <is>
+          <t>0.1896±0.0661</t>
+        </is>
+      </c>
+      <c r="AG13" t="inlineStr">
+        <is>
+          <t>0.1725±0.0321</t>
+        </is>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>0.0185±0.0031</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>0.0170±0.0041</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>0.0189±0.0045</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>0.0289±0.0063</t>
+        </is>
+      </c>
+      <c r="AL13" t="inlineStr">
+        <is>
+          <t>1.0000±0.0000</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>1.0000±0.0000</t>
+        </is>
+      </c>
+      <c r="AN13" t="inlineStr">
+        <is>
+          <t>1.0000±0.0000</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>1.0000±0.0000</t>
+        </is>
+      </c>
+      <c r="AP13" t="inlineStr">
+        <is>
+          <t>0.1175±0.0195</t>
+        </is>
+      </c>
+      <c r="AQ13" t="inlineStr">
+        <is>
+          <t>0.1087±0.0205</t>
+        </is>
+      </c>
+      <c r="AR13" t="inlineStr">
+        <is>
+          <t>0.1122±0.0240</t>
+        </is>
+      </c>
+      <c r="AS13" t="inlineStr">
+        <is>
+          <t>0.1485±0.0244</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr">
+        <is>
+          <t>0.6710±0.0606</t>
+        </is>
+      </c>
+      <c r="AU13" t="inlineStr">
+        <is>
+          <t>0.6622±0.0632</t>
+        </is>
+      </c>
+      <c r="AV13" t="inlineStr">
+        <is>
+          <t>0.6327±0.0585</t>
+        </is>
+      </c>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>0.5394±0.0490</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>0.0644±0.0112</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>0.0593±0.0118</t>
+        </is>
+      </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>0.0619±0.0143</t>
+        </is>
+      </c>
+      <c r="BA13" t="inlineStr">
+        <is>
+          <t>0.0865±0.0160</t>
+        </is>
+      </c>
+      <c r="BB13" t="inlineStr">
+        <is>
+          <t>0.0654±0.0091</t>
+        </is>
+      </c>
+      <c r="BC13" t="inlineStr">
+        <is>
+          <t>0.0588±0.0101</t>
+        </is>
+      </c>
+      <c r="BD13" t="inlineStr">
+        <is>
+          <t>0.0601±0.0116</t>
+        </is>
+      </c>
+      <c r="BE13" t="inlineStr">
+        <is>
+          <t>0.0805±0.0122</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>lp</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>0.8121±0.0088</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>0.8214±0.0193</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>0.6387±0.0297</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>0.3630±0.0321</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>0.4374±0.0148</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>0.3579±0.0221</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>0.1801±0.0136</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>0.1124±0.0063</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>0.3905±0.0176</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>0.3344±0.0219</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>0.3218±0.0111</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>0.3941±0.0137</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>0.4053±0.0163</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>0.3355±0.0215</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>0.2100±0.0097</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>0.1648±0.0074</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>0.9064±0.0030</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>0.8948±0.0042</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>0.8014±0.0087</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>0.6690±0.0067</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>0.3895±0.0168</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>0.3148±0.0213</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>0.1624±0.0113</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>0.1067±0.0058</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>0.1547±0.0024</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>0.1303±0.0130</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>0.1237±0.0070</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>0.1253±0.0054</t>
+        </is>
+      </c>
+      <c r="AD14" t="inlineStr">
+        <is>
+          <t>0.2095±0.0482</t>
+        </is>
+      </c>
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t>0.1622±0.0232</t>
+        </is>
+      </c>
+      <c r="AF14" t="inlineStr">
+        <is>
+          <t>0.1021±0.0059</t>
+        </is>
+      </c>
+      <c r="AG14" t="inlineStr">
+        <is>
+          <t>0.0918±0.0033</t>
+        </is>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>0.1529±0.0044</t>
+        </is>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>0.1279±0.0110</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>0.1987±0.0258</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>0.3303±0.0402</t>
+        </is>
+      </c>
+      <c r="AL14" t="inlineStr">
+        <is>
+          <t>1.0000±0.0000</t>
+        </is>
+      </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>0.9997±0.0006</t>
+        </is>
+      </c>
+      <c r="AN14" t="inlineStr">
+        <is>
+          <t>0.9058±0.0130</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>0.6665±0.0700</t>
+        </is>
+      </c>
+      <c r="AP14" t="inlineStr">
+        <is>
+          <t>0.4022±0.0165</t>
+        </is>
+      </c>
+      <c r="AQ14" t="inlineStr">
+        <is>
+          <t>0.3456±0.0209</t>
+        </is>
+      </c>
+      <c r="AR14" t="inlineStr">
+        <is>
+          <t>0.2133±0.0091</t>
+        </is>
+      </c>
+      <c r="AS14" t="inlineStr">
+        <is>
+          <t>0.1674±0.0064</t>
+        </is>
+      </c>
+      <c r="AT14" t="inlineStr">
+        <is>
+          <t>0.4378±0.0153</t>
+        </is>
+      </c>
+      <c r="AU14" t="inlineStr">
+        <is>
+          <t>0.3654±0.0222</t>
+        </is>
+      </c>
+      <c r="AV14" t="inlineStr">
+        <is>
+          <t>0.1607±0.0089</t>
+        </is>
+      </c>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>0.1064±0.0042</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>0.3721±0.0173</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>0.3280±0.0217</t>
+        </is>
+      </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>0.3176±0.0102</t>
+        </is>
+      </c>
+      <c r="BA14" t="inlineStr">
+        <is>
+          <t>0.3931±0.0132</t>
+        </is>
+      </c>
+      <c r="BB14" t="inlineStr">
+        <is>
+          <t>0.3438±0.0190</t>
+        </is>
+      </c>
+      <c r="BC14" t="inlineStr">
+        <is>
+          <t>0.2556±0.0215</t>
+        </is>
+      </c>
+      <c r="BD14" t="inlineStr">
+        <is>
+          <t>0.0549±0.0159</t>
+        </is>
+      </c>
+      <c r="BE14" t="inlineStr">
+        <is>
+          <t>0.0066±0.0042</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>mlknn</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>0.8904±0.0211</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>0.8822±0.0207</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>0.8291±0.0308</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>0.6857±0.0493</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>0.2120±0.0244</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>0.2042±0.0323</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>0.1953±0.0287</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>0.1654±0.0212</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>0.1980±0.0203</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>0.1994±0.0321</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>0.2206±0.0381</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>0.2928±0.0444</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>0.2000±0.0212</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>0.1954±0.0309</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>0.1973±0.0305</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>0.1956±0.0261</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>0.9151±0.0020</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>0.9079±0.0028</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>0.8883±0.0063</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>0.8233±0.0098</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>0.1906±0.0193</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>0.1826±0.0286</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>0.1761±0.0259</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>0.1521±0.0198</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>0.1233±0.0230</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>0.1132±0.0176</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>0.1208±0.0144</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>0.1250±0.0136</t>
+        </is>
+      </c>
+      <c r="AD15" t="inlineStr">
+        <is>
+          <t>0.2793±0.0612</t>
+        </is>
+      </c>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t>0.2058±0.0334</t>
+        </is>
+      </c>
+      <c r="AF15" t="inlineStr">
+        <is>
+          <t>0.1540±0.0199</t>
+        </is>
+      </c>
+      <c r="AG15" t="inlineStr">
+        <is>
+          <t>0.1130±0.0074</t>
+        </is>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>0.0879±0.0179</t>
+        </is>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>0.0871±0.0162</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>0.1161±0.0235</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>0.1820±0.0364</t>
+        </is>
+      </c>
+      <c r="AL15" t="inlineStr">
+        <is>
+          <t>1.0000±0.0000</t>
+        </is>
+      </c>
+      <c r="AM15" t="inlineStr">
+        <is>
+          <t>1.0000±0.0000</t>
+        </is>
+      </c>
+      <c r="AN15" t="inlineStr">
+        <is>
+          <t>0.9985±0.0026</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>0.9570±0.0152</t>
+        </is>
+      </c>
+      <c r="AP15" t="inlineStr">
+        <is>
+          <t>0.2733±0.0216</t>
+        </is>
+      </c>
+      <c r="AQ15" t="inlineStr">
+        <is>
+          <t>0.2591±0.0294</t>
+        </is>
+      </c>
+      <c r="AR15" t="inlineStr">
+        <is>
+          <t>0.2434±0.0306</t>
+        </is>
+      </c>
+      <c r="AS15" t="inlineStr">
+        <is>
+          <t>0.2138±0.0228</t>
+        </is>
+      </c>
+      <c r="AT15" t="inlineStr">
+        <is>
+          <t>0.4979±0.0180</t>
+        </is>
+      </c>
+      <c r="AU15" t="inlineStr">
+        <is>
+          <t>0.4080±0.0245</t>
+        </is>
+      </c>
+      <c r="AV15" t="inlineStr">
+        <is>
+          <t>0.2870±0.0273</t>
+        </is>
+      </c>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>0.1718±0.0155</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>0.1892±0.0216</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>0.1916±0.0313</t>
+        </is>
+      </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>0.2138±0.0385</t>
+        </is>
+      </c>
+      <c r="BA15" t="inlineStr">
+        <is>
+          <t>0.2853±0.0442</t>
+        </is>
+      </c>
+      <c r="BB15" t="inlineStr">
+        <is>
+          <t>0.1632±0.0142</t>
+        </is>
+      </c>
+      <c r="BC15" t="inlineStr">
+        <is>
+          <t>0.1457±0.0227</t>
+        </is>
+      </c>
+      <c r="BD15" t="inlineStr">
+        <is>
+          <t>0.1180±0.0165</t>
+        </is>
+      </c>
+      <c r="BE15" t="inlineStr">
+        <is>
+          <t>0.0518±0.0083</t>
         </is>
       </c>
     </row>
